--- a/docs/Fill_Up_Template/구매단가관리_업로드양식.xlsx
+++ b/docs/Fill_Up_Template/구매단가관리_업로드양식.xlsx
@@ -457,12 +457,12 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -536,7 +536,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G:국내구매</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F:고정단가</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Y:유상사급</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T:임시단가</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P:도입(과세)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F:고정단가</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F:무상구매</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F:고정단가</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -712,14 +712,14 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="D2:D2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 선택하세요" prompt="A=외부부품 D=도입(면세) F=무상구매 G=국내구매 L=도입로칼 M=무상사급 N=내부거래 O=OEM P=도입(과세) T=자작 Y=유상사급" type="list">
-      <formula1>"A,D,F,G,L,M,N,O,P,T,Y"</formula1>
+    <dataValidation sqref="D2:D2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 선택하세요" prompt="코드:코드값 선택 (업로드 시 : 앞 코드만 반영)" type="list">
+      <formula1>"A:외부부품,D:도입(면세),F:무상구매,G:국내구매,L:도입로칼,M:무상사급,N:내부거래,O:OEM,P:도입(과세),T:자작,Y:유상사급"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 선택하세요" prompt="KRW=원화 USD=달러 JPY=엔화 CNY=인민폐 HKD=홍콩달러 VND=동" type="list">
       <formula1>"KRW,USD,JPY,CNY,HKD,VND"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 선택하세요" prompt="F=고정단가 T=임시단가" type="list">
-      <formula1>"F,T"</formula1>
+    <dataValidation sqref="I2:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 선택하세요" prompt="코드:코드값 선택 (업로드 시 : 앞 코드만 반영)" type="list">
+      <formula1>"F:고정단가,T:임시단가"</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 선택하세요" prompt="1=수출 2=내수" type="list">
       <formula1>"1,2"</formula1>
@@ -735,13 +735,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -828,7 +828,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>공급사코드에 대응(입력 편의용, 검증 기준은 공급사코드)</t>
+          <t>공급사코드에 대응(입력 편의용)</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A/D/F/G/L/M/N/O/P/T/Y</t>
+          <t>코드:코드값 (드롭다운)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A=외부부품, D=도입(면세), F=무상구매, G=국내구매, L=도입로칼, M=무상사급, N=내부거래, O=OEM, P=도입(과세), T=자작, Y=유상사급 (드롭다운)</t>
+          <t>A:외부부품 D:도입(면세) F:무상구매 G:국내구매 L:도입로칼 M:무상사급 N:내부거래 O:OEM P:도입(과세) T:자작 Y:유상사급 — 업로드 시 콜론(:) 앞 코드만 저장</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KRW=원화, USD=달러, JPY=엔화, CNY=인민폐, HKD=홍콩달러, VND=동 (드롭다운)</t>
+          <t>KRW=원화 USD=달러 JPY=엔화 CNY=인민폐 HKD=홍콩달러 VND=동 (드롭다운)</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>F/T</t>
+          <t>코드:코드값 (드롭다운)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>F=고정단가, T=임시단가 (드롭다운)</t>
+          <t>F:고정단가 T:임시단가 — 업로드 시 콜론(:) 앞 코드만 저장</t>
         </is>
       </c>
     </row>
@@ -982,19 +982,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1=수출, 2=내수 (드롭다운)</t>
+          <t>1=수출 2=내수 (드롭다운)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>※ 대상 테이블: IM_ITEM_UNIT_PRICE (품목코드+공급사코드+구입유형+시작일+조직 = 복합키)</t>
+          <t>※ 구입유형·단가유형은 셀에 '코드:코드값'으로 선택하지만, 업로드 시 시스템이 콜론(:) 앞 코드만 반영합니다.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>※ 대상 테이블: IM_ITEM_UNIT_PRICE (품목+공급사+구입유형+시작일+조직 = 복합키)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
